--- a/data/base/Backlog_25.xlsx
+++ b/data/base/Backlog_25.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FBCB7-02C9-43F3-B291-84C8F614FFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{873FCBA5-9B61-4961-95BC-9946612591D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="31">
   <si>
     <t>Status</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>Patrick Doyle</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -676,18 +679,18 @@
         <v>46206</v>
       </c>
       <c r="G2" s="5">
-        <v>18911</v>
+        <v>19321</v>
       </c>
       <c r="H2" s="12">
-        <v>46188.448159722226</v>
+        <v>46195.670243055552</v>
       </c>
       <c r="I2" s="16">
         <v>46202</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -711,16 +714,16 @@
         <v>46206</v>
       </c>
       <c r="G3" s="5">
-        <v>19321</v>
+        <v>19362</v>
       </c>
       <c r="H3" s="12">
-        <v>46195.670243055552</v>
+        <v>46195.438668981478</v>
       </c>
       <c r="I3" s="16">
         <v>46202</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>12</v>
@@ -746,10 +749,10 @@
         <v>46206</v>
       </c>
       <c r="G4" s="5">
-        <v>19362</v>
+        <v>19389</v>
       </c>
       <c r="H4" s="12">
-        <v>46195.438668981478</v>
+        <v>46196.608472222222</v>
       </c>
       <c r="I4" s="16">
         <v>46202</v>
@@ -766,7 +769,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5">
         <v>2026</v>
@@ -781,10 +784,10 @@
         <v>46206</v>
       </c>
       <c r="G5" s="5">
-        <v>19389</v>
+        <v>18911</v>
       </c>
       <c r="H5" s="12">
-        <v>46196.608472222222</v>
+        <v>46188.448159722226</v>
       </c>
       <c r="I5" s="16">
         <v>46202</v>
@@ -792,7 +795,7 @@
       <c r="J5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -825,7 +828,7 @@
         <v>46202</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>12</v>
@@ -895,7 +898,7 @@
         <v>46202</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>12</v>
@@ -1000,7 +1003,7 @@
         <v>46202</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>12</v>
@@ -1035,7 +1038,7 @@
         <v>46202</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>12</v>
@@ -1140,7 +1143,7 @@
         <v>46202</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>12</v>
@@ -1183,7 +1186,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K18" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
       <sortCondition ref="B1:B18"/>
     </sortState>
   </autoFilter>
@@ -1275,7 +1278,7 @@
         <v>46202</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>1</v>
@@ -1310,7 +1313,7 @@
         <v>46202</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>1</v>
@@ -1345,7 +1348,7 @@
         <v>46202</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>1</v>
@@ -1380,7 +1383,7 @@
         <v>46202</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>1</v>
@@ -1415,7 +1418,7 @@
         <v>46202</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>1</v>
@@ -1450,7 +1453,7 @@
         <v>46202</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>1</v>
@@ -1485,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>1</v>
@@ -1520,7 +1523,7 @@
         <v>46202</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>1</v>
@@ -1555,7 +1558,7 @@
         <v>46202</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>1</v>
@@ -1590,7 +1593,7 @@
         <v>46202</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>1</v>
@@ -1601,7 +1604,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" s="10">
         <v>2026</v>
@@ -1695,7 +1698,7 @@
         <v>46202</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>1</v>
@@ -1730,7 +1733,7 @@
         <v>46202</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>1</v>
@@ -1741,7 +1744,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" s="10">
         <v>2026</v>
@@ -1835,7 +1838,7 @@
         <v>46202</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>1</v>
@@ -1870,20 +1873,20 @@
         <v>46202</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="10">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5">
         <v>2026</v>
       </c>
       <c r="D20" s="10">
@@ -1895,30 +1898,30 @@
       <c r="F20" s="16">
         <v>46206</v>
       </c>
-      <c r="G20" s="10">
-        <v>17306</v>
-      </c>
-      <c r="H20" s="17">
-        <v>46164.428784722222</v>
+      <c r="G20" s="5">
+        <v>18346</v>
+      </c>
+      <c r="H20" s="12">
+        <v>46178.538541666669</v>
       </c>
       <c r="I20" s="16">
         <v>46202</v>
       </c>
-      <c r="J20" s="10" t="s">
-        <v>13</v>
+      <c r="J20" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="10">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5">
         <v>2026</v>
       </c>
       <c r="D21" s="10">
@@ -1930,17 +1933,17 @@
       <c r="F21" s="16">
         <v>46206</v>
       </c>
-      <c r="G21" s="10">
-        <v>19359</v>
-      </c>
-      <c r="H21" s="17">
-        <v>46199.508842592593</v>
+      <c r="G21" s="5">
+        <v>18418</v>
+      </c>
+      <c r="H21" s="12">
+        <v>46178.708333333336</v>
       </c>
       <c r="I21" s="16">
         <v>46202</v>
       </c>
-      <c r="J21" s="10" t="s">
-        <v>13</v>
+      <c r="J21" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>1</v>
@@ -1951,7 +1954,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C22" s="10">
         <v>2026</v>
@@ -1966,10 +1969,10 @@
         <v>46206</v>
       </c>
       <c r="G22" s="10">
-        <v>19407</v>
+        <v>17306</v>
       </c>
       <c r="H22" s="17">
-        <v>46195.686493055553</v>
+        <v>46164.428784722222</v>
       </c>
       <c r="I22" s="16">
         <v>46202</v>
@@ -1986,7 +1989,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="10">
         <v>2026</v>
@@ -2001,10 +2004,10 @@
         <v>46206</v>
       </c>
       <c r="G23" s="10">
-        <v>17195</v>
+        <v>19359</v>
       </c>
       <c r="H23" s="17">
-        <v>46165.999988425923</v>
+        <v>46199.508842592593</v>
       </c>
       <c r="I23" s="16">
         <v>46202</v>
@@ -2021,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C24" s="10">
         <v>2026</v>
@@ -2036,16 +2039,16 @@
         <v>46206</v>
       </c>
       <c r="G24" s="10">
-        <v>17382</v>
+        <v>19407</v>
       </c>
       <c r="H24" s="17">
-        <v>46167.708333333336</v>
+        <v>46195.686493055553</v>
       </c>
       <c r="I24" s="16">
         <v>46202</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>1</v>
@@ -2071,10 +2074,10 @@
         <v>46206</v>
       </c>
       <c r="G25" s="10">
-        <v>18490</v>
+        <v>17195</v>
       </c>
       <c r="H25" s="17">
-        <v>46178.640798611108</v>
+        <v>46165.999988425923</v>
       </c>
       <c r="I25" s="16">
         <v>46202</v>
@@ -2106,10 +2109,10 @@
         <v>46206</v>
       </c>
       <c r="G26" s="10">
-        <v>18626</v>
+        <v>17382</v>
       </c>
       <c r="H26" s="17">
-        <v>46184.449097222219</v>
+        <v>46167.708333333336</v>
       </c>
       <c r="I26" s="16">
         <v>46202</v>
@@ -2141,10 +2144,10 @@
         <v>46206</v>
       </c>
       <c r="G27" s="10">
-        <v>18649</v>
+        <v>18490</v>
       </c>
       <c r="H27" s="17">
-        <v>46184.400578703702</v>
+        <v>46178.640798611108</v>
       </c>
       <c r="I27" s="16">
         <v>46202</v>
@@ -2161,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C28" s="10">
         <v>2026</v>
@@ -2176,10 +2179,10 @@
         <v>46206</v>
       </c>
       <c r="G28" s="10">
-        <v>19657</v>
+        <v>18626</v>
       </c>
       <c r="H28" s="17">
-        <v>46199.453206018516</v>
+        <v>46184.449097222219</v>
       </c>
       <c r="I28" s="16">
         <v>46202</v>
@@ -2196,7 +2199,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C29" s="10">
         <v>2026</v>
@@ -2211,10 +2214,10 @@
         <v>46206</v>
       </c>
       <c r="G29" s="10">
-        <v>19671</v>
+        <v>18649</v>
       </c>
       <c r="H29" s="17">
-        <v>46202.553229166668</v>
+        <v>46184.400578703702</v>
       </c>
       <c r="I29" s="16">
         <v>46202</v>
@@ -2231,7 +2234,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C30" s="10">
         <v>2026</v>
@@ -2246,10 +2249,10 @@
         <v>46206</v>
       </c>
       <c r="G30" s="10">
-        <v>19195</v>
+        <v>19657</v>
       </c>
       <c r="H30" s="17">
-        <v>46192.573078703703</v>
+        <v>46199.453206018516</v>
       </c>
       <c r="I30" s="16">
         <v>46202</v>
@@ -2266,7 +2269,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C31" s="10">
         <v>2026</v>
@@ -2281,16 +2284,16 @@
         <v>46206</v>
       </c>
       <c r="G31" s="10">
-        <v>19530</v>
+        <v>19671</v>
       </c>
       <c r="H31" s="17">
-        <v>46202.505532407406</v>
+        <v>46202.553229166668</v>
       </c>
       <c r="I31" s="16">
         <v>46202</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>1</v>
@@ -2301,7 +2304,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C32" s="10">
         <v>2026</v>
@@ -2316,16 +2319,16 @@
         <v>46206</v>
       </c>
       <c r="G32" s="10">
-        <v>19631</v>
+        <v>19195</v>
       </c>
       <c r="H32" s="17">
-        <v>46198.595671296294</v>
+        <v>46192.573078703703</v>
       </c>
       <c r="I32" s="16">
         <v>46202</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>1</v>
@@ -2336,7 +2339,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C33" s="10">
         <v>2026</v>
@@ -2351,16 +2354,16 @@
         <v>46206</v>
       </c>
       <c r="G33" s="10">
-        <v>18188</v>
+        <v>19530</v>
       </c>
       <c r="H33" s="17">
-        <v>46177.373287037037</v>
+        <v>46202.505532407406</v>
       </c>
       <c r="I33" s="16">
         <v>46202</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>1</v>
@@ -2371,7 +2374,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C34" s="10">
         <v>2026</v>
@@ -2386,10 +2389,10 @@
         <v>46206</v>
       </c>
       <c r="G34" s="10">
-        <v>18650</v>
+        <v>19631</v>
       </c>
       <c r="H34" s="17">
-        <v>46184.528078703705</v>
+        <v>46198.595671296294</v>
       </c>
       <c r="I34" s="16">
         <v>46202</v>
@@ -2421,10 +2424,10 @@
         <v>46206</v>
       </c>
       <c r="G35" s="10">
-        <v>19257</v>
+        <v>18188</v>
       </c>
       <c r="H35" s="17">
-        <v>46195.362511574072</v>
+        <v>46177.373287037037</v>
       </c>
       <c r="I35" s="16">
         <v>46202</v>
@@ -2456,10 +2459,10 @@
         <v>46206</v>
       </c>
       <c r="G36" s="10">
-        <v>19444</v>
+        <v>18650</v>
       </c>
       <c r="H36" s="17">
-        <v>46197.487592592595</v>
+        <v>46184.528078703705</v>
       </c>
       <c r="I36" s="16">
         <v>46202</v>
@@ -2491,94 +2494,94 @@
         <v>46206</v>
       </c>
       <c r="G37" s="10">
+        <v>19257</v>
+      </c>
+      <c r="H37" s="17">
+        <v>46195.362511574072</v>
+      </c>
+      <c r="I37" s="16">
+        <v>46202</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="10">
+        <v>25</v>
+      </c>
+      <c r="E38" s="16">
+        <v>46202</v>
+      </c>
+      <c r="F38" s="16">
+        <v>46206</v>
+      </c>
+      <c r="G38" s="10">
+        <v>19444</v>
+      </c>
+      <c r="H38" s="17">
+        <v>46197.487592592595</v>
+      </c>
+      <c r="I38" s="16">
+        <v>46202</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D39" s="10">
+        <v>25</v>
+      </c>
+      <c r="E39" s="16">
+        <v>46202</v>
+      </c>
+      <c r="F39" s="16">
+        <v>46206</v>
+      </c>
+      <c r="G39" s="10">
         <v>19522</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H39" s="17">
         <v>46197.613125000003</v>
       </c>
-      <c r="I37" s="16">
-        <v>46202</v>
-      </c>
-      <c r="J37" s="10" t="s">
+      <c r="I39" s="16">
+        <v>46202</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K37" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D38" s="10">
-        <v>25</v>
-      </c>
-      <c r="E38" s="16">
-        <v>46202</v>
-      </c>
-      <c r="F38" s="16">
-        <v>46206</v>
-      </c>
-      <c r="G38" s="5">
-        <v>18346</v>
-      </c>
-      <c r="H38" s="12">
-        <v>46178.538541666669</v>
-      </c>
-      <c r="I38" s="16">
-        <v>46202</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="5">
-        <v>2026</v>
-      </c>
-      <c r="D39" s="10">
-        <v>25</v>
-      </c>
-      <c r="E39" s="16">
-        <v>46202</v>
-      </c>
-      <c r="F39" s="16">
-        <v>46206</v>
-      </c>
-      <c r="G39" s="5">
-        <v>18418</v>
-      </c>
-      <c r="H39" s="12">
-        <v>46178.708333333336</v>
-      </c>
-      <c r="I39" s="16">
-        <v>46202</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>12</v>
+      <c r="K39" s="10" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K27" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K39">
       <sortCondition ref="B1:B27"/>
     </sortState>
   </autoFilter>
